--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251008_201152.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251008_201152.xlsx
@@ -5086,7 +5086,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251008_201152.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251008_201152.xlsx
@@ -5086,7 +5086,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
